--- a/preorder_forms/027_school_lunch_preorder_form--preorder_forms.xlsx
+++ b/preorder_forms/027_school_lunch_preorder_form--preorder_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1116,80 +1116,80 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fruits</t>
+          <t>sugars</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fruits</t>
+          <t>Sugars</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>daily_menu_choices</t>
+          <t>student_diet_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>grains</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Grains</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>daily_menu_choices</t>
+          <t>student_diet_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sugars</t>
+          <t>non-vegetarian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sugars</t>
+          <t>Non-Vegetarian</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>student_diet_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>vegetarian</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>student_diet_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>non-vegetarian</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Non-Vegetarian</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1201,44 +1201,10 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>credit_card</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Credit Card</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>check</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
